--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Easthill_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Easthill_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,6 +737,174 @@
         <v>34.79</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>99482</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sparkling Ice - Orange Mango</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>99458</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sparkling Ice - Kiwi Strawberry</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12.19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>99402</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sparkling Ice - Black Raspberry</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13.54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AT104</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Simply - Orange</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="E19" t="n">
+        <v>182.16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AH252</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Juice</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TN454</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Mango</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TN362</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Pineapple</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E22" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TN380</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Natalie's - Strawberry Lemonade</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
